--- a/mapping/SB_DWH/Mapping_DIM_RLOS_APPLICATION.xlsx
+++ b/mapping/SB_DWH/Mapping_DIM_RLOS_APPLICATION.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variable" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping'!$A$5:$E$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping'!$A$6:$E$71</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
@@ -230,7 +230,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -307,9 +307,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -362,9 +359,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -693,7 +687,7 @@
     <col width="29.6640625" customWidth="1" style="7" min="1" max="1"/>
     <col width="20.5" customWidth="1" style="7" min="2" max="2"/>
     <col width="27.6640625" customWidth="1" style="1" min="3" max="3"/>
-    <col width="37" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="52.1640625" customWidth="1" style="2" min="4" max="4"/>
     <col width="50.33203125" customWidth="1" style="7" min="5" max="5"/>
     <col width="48.5" customWidth="1" style="2" min="6" max="6"/>
     <col width="9.1640625" customWidth="1" style="7" min="7" max="16384"/>
@@ -710,12 +704,12 @@
           <t>DIM_RLOS_APPLICATION</t>
         </is>
       </c>
-      <c r="E1" s="43" t="inlineStr">
+      <c r="E1" s="42" t="inlineStr">
         <is>
           <t>NG_SB_RLOS_EXTTABLE AS A</t>
         </is>
       </c>
-      <c r="F1" s="43" t="n"/>
+      <c r="F1" s="42" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -728,102 +722,108 @@
           <t>Bảng chiều hồ sơ tín dụng RLOS, driving từ NG_SB_RLOS_EXTTABLE, bổ sung thuộc tính từ nhiều bảng phụ trợ</t>
         </is>
       </c>
-      <c r="E2" s="43" t="inlineStr">
+      <c r="E2" s="42" t="inlineStr">
         <is>
           <t>NG_SB_RLOS_APPROVAL AS B</t>
         </is>
       </c>
-      <c r="F2" s="43" t="n"/>
+      <c r="F2" s="42" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Primary Key</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Bao gồm các trường màu đỏ</t>
-        </is>
-      </c>
-      <c r="E3" s="43" t="inlineStr">
+          <t>DIMENSION_KEY</t>
+        </is>
+      </c>
+      <c r="E3" s="42" t="inlineStr">
         <is>
           <t>NG_SB_RLOS_APPLICANT_GENERAL AS C</t>
         </is>
       </c>
-      <c r="F3" s="43" t="n"/>
+      <c r="F3" s="42" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Business Key</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>WI_NAME</t>
+        </is>
+      </c>
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>NG_SB_RLOS_ENTRY_EXIT AS D</t>
         </is>
       </c>
-      <c r="F4" s="43" t="n"/>
+      <c r="F4" s="42" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="44" t="n"/>
-      <c r="D5" s="44" t="n"/>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="42" t="inlineStr">
         <is>
           <t>NG_SB_RLOS_SENT_CBS_LOG AS E</t>
         </is>
       </c>
-      <c r="F5" s="43" t="n"/>
+      <c r="F5" s="42" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="44" t="n"/>
-      <c r="D6" s="44" t="n"/>
-      <c r="E6" s="43" t="inlineStr">
+      <c r="C6" s="43" t="n"/>
+      <c r="D6" s="43" t="n"/>
+      <c r="E6" s="42" t="inlineStr">
         <is>
           <t>NG_SB_RLOS_CREDIT_PROPOSAL AS F</t>
         </is>
       </c>
-      <c r="F6" s="43" t="n"/>
+      <c r="F6" s="42" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
       <c r="B7" s="6" t="n"/>
-      <c r="C7" s="44" t="n"/>
-      <c r="D7" s="44" t="n"/>
-      <c r="E7" s="43" t="inlineStr">
+      <c r="C7" s="43" t="n"/>
+      <c r="D7" s="43" t="n"/>
+      <c r="E7" s="42" t="inlineStr">
         <is>
           <t>NG_SB_RLOS_CREDIT_PROPOSAL_APP AS G</t>
         </is>
       </c>
-      <c r="F7" s="43" t="n"/>
+      <c r="F7" s="42" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="44" t="n"/>
-      <c r="D8" s="44" t="n"/>
-      <c r="E8" s="43" t="inlineStr">
+      <c r="C8" s="43" t="n"/>
+      <c r="D8" s="43" t="n"/>
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>NG_SB_RLOS_REPAY_CALC AS H</t>
         </is>
       </c>
-      <c r="F8" s="43" t="n"/>
+      <c r="F8" s="42" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="44" t="n"/>
-      <c r="D9" s="44" t="n"/>
-      <c r="E9" s="43" t="inlineStr">
+      <c r="C9" s="43" t="n"/>
+      <c r="D9" s="43" t="n"/>
+      <c r="E9" s="42" t="inlineStr">
         <is>
           <t>NG_SB_RLOS_REPAYFLAGS AS I</t>
         </is>
       </c>
-      <c r="F9" s="43" t="n"/>
-    </row>
-    <row r="10" ht="17" customFormat="1" customHeight="1" s="5">
+      <c r="F9" s="42" t="n"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Column name</t>
@@ -851,7 +851,7 @@
       </c>
       <c r="F10" s="25" t="n"/>
     </row>
-    <row r="11" ht="17" customHeight="1">
+    <row r="11" ht="17" customFormat="1" customHeight="1" s="5">
       <c r="A11" s="23" t="n"/>
       <c r="B11" s="23" t="n"/>
       <c r="C11" s="23" t="n"/>
@@ -863,18 +863,18 @@
       <c r="E11" s="24" t="n"/>
       <c r="F11" s="24" t="n"/>
     </row>
-    <row r="12" ht="51" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>Surrogate Key</t>
         </is>
@@ -889,20 +889,20 @@
           <t>Sinh bằng Oracle sequence tại SB_DWH</t>
         </is>
       </c>
-      <c r="F12" s="31" t="n"/>
-    </row>
-    <row r="13" ht="51" customHeight="1">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="F12" s="30" t="n"/>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>APPLICATION_SK</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>Khóa tham chiếu DIM_RLOS_APPLICATION</t>
         </is>
@@ -917,20 +917,20 @@
           <t>Sinh bằng Oracle sequence tại SB_DWH</t>
         </is>
       </c>
-      <c r="F13" s="31" t="n"/>
-    </row>
-    <row r="14" ht="51" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="F13" s="30" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>WI_NAME</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>Mã hồ sơ tín dụng RLOS</t>
         </is>
@@ -945,20 +945,20 @@
           <t>A.WI_NAME</t>
         </is>
       </c>
-      <c r="F14" s="31" t="n"/>
-    </row>
-    <row r="15" ht="51" customHeight="1">
-      <c r="A15" s="45" t="inlineStr">
+      <c r="F14" s="30" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>LOANCASEID</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>Mã khoản vay</t>
         </is>
@@ -973,20 +973,20 @@
           <t>A.LOANCASEID</t>
         </is>
       </c>
-      <c r="F15" s="31" t="n"/>
-    </row>
-    <row r="16" ht="51" customHeight="1">
-      <c r="A16" s="45" t="inlineStr">
+      <c r="F15" s="30" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>STREAM</t>
         </is>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>Luồng nghiệp vụ</t>
         </is>
@@ -1001,20 +1001,20 @@
           <t>B.STREAM</t>
         </is>
       </c>
-      <c r="F16" s="31" t="n"/>
-    </row>
-    <row r="17" ht="51" customHeight="1">
-      <c r="A17" s="45" t="inlineStr">
+      <c r="F16" s="30" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>POLICY</t>
         </is>
       </c>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>Chính sách tín dụng</t>
         </is>
@@ -1029,20 +1029,20 @@
           <t>C.POLICY</t>
         </is>
       </c>
-      <c r="F17" s="31" t="n"/>
-    </row>
-    <row r="18" ht="51" customHeight="1">
-      <c r="A18" s="45" t="inlineStr">
+      <c r="F17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>CAMPAIGN</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C18" s="31" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>Chương trình bán</t>
         </is>
@@ -1057,20 +1057,20 @@
           <t>C.CAMPAIGN</t>
         </is>
       </c>
-      <c r="F18" s="31" t="n"/>
-    </row>
-    <row r="19" ht="51" customHeight="1">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="F18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>PROOF_OF_INCOME</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C19" s="31" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>Hình thức chứng minh thu nhập</t>
         </is>
@@ -1085,20 +1085,20 @@
           <t>C.PROOF_OF_INCOME</t>
         </is>
       </c>
-      <c r="F19" s="31" t="n"/>
-    </row>
-    <row r="20" ht="51" customHeight="1">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="F19" s="30" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>COLL_REQUIRE</t>
         </is>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C20" s="31" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>Yêu cầu tài sản bảo đảm</t>
         </is>
@@ -1113,20 +1113,20 @@
           <t>C.COLLREQUIRE</t>
         </is>
       </c>
-      <c r="F20" s="31" t="n"/>
-    </row>
-    <row r="21" ht="51" customHeight="1">
-      <c r="A21" s="45" t="inlineStr">
+      <c r="F20" s="30" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>IS_SEC_PRODUCT</t>
         </is>
       </c>
-      <c r="B21" s="27" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C21" s="31" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>Có sản phẩm phụ</t>
         </is>
@@ -1141,20 +1141,20 @@
           <t>C.IS_SEC_PRODUCT</t>
         </is>
       </c>
-      <c r="F21" s="31" t="n"/>
-    </row>
-    <row r="22" ht="51" customHeight="1">
-      <c r="A22" s="45" t="inlineStr">
+      <c r="F21" s="30" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>DEVIATION_FLAG</t>
         </is>
       </c>
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C22" s="31" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
         <is>
           <t>Có ngoại lệ chính sách</t>
         </is>
@@ -1169,20 +1169,20 @@
           <t>C.DEVIATION_FLAG</t>
         </is>
       </c>
-      <c r="F22" s="31" t="n"/>
-    </row>
-    <row r="23" ht="51" customHeight="1">
-      <c r="A23" s="45" t="inlineStr">
+      <c r="F22" s="30" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>CREATE_EMPLOYEE_CODE</t>
         </is>
       </c>
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C23" s="31" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
         <is>
           <t>Mã cán bộ quản lý hồ sơ</t>
         </is>
@@ -1197,20 +1197,20 @@
           <t>C.EMPLOYEE_CODE</t>
         </is>
       </c>
-      <c r="F23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="51" customHeight="1">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="F23" s="30" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>CREATE_EMPLOYEE_NAME</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C24" s="31" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
         <is>
           <t>Tên cán bộ quản lý hồ sơ</t>
         </is>
@@ -1225,20 +1225,20 @@
           <t>C.EMPLOYEE_NAME</t>
         </is>
       </c>
-      <c r="F24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="51" customHeight="1">
-      <c r="A25" s="45" t="inlineStr">
+      <c r="F24" s="30" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>CREATION_DATE</t>
         </is>
       </c>
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C25" s="31" t="inlineStr">
+      <c r="C25" s="30" t="inlineStr">
         <is>
           <t>Ngày khởi tạo hồ sơ</t>
         </is>
@@ -1253,20 +1253,20 @@
           <t>TRUNC(MIN(D.ENTRYDATE)) theo A.WI_NAME</t>
         </is>
       </c>
-      <c r="F25" s="31" t="n"/>
-    </row>
-    <row r="26" ht="51" customHeight="1">
-      <c r="A26" s="45" t="inlineStr">
+      <c r="F25" s="30" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>APPLICATION_DATE</t>
         </is>
       </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
         <is>
           <t>Ngày khởi tạo theo form</t>
         </is>
@@ -1281,20 +1281,20 @@
           <t>C.APPLICATION_DATE</t>
         </is>
       </c>
-      <c r="F26" s="31" t="n"/>
-    </row>
-    <row r="27" ht="51" customHeight="1">
-      <c r="A27" s="45" t="inlineStr">
+      <c r="F26" s="30" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>RESULT_MAIN_CARD_ID</t>
         </is>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C27" s="31" t="inlineStr">
+      <c r="C27" s="30" t="inlineStr">
         <is>
           <t>Mã thẻ chính (T24)</t>
         </is>
@@ -1309,20 +1309,20 @@
           <t>E.RESULT_SEAB_MAIN_CARD_ID</t>
         </is>
       </c>
-      <c r="F27" s="31" t="n"/>
-    </row>
-    <row r="28" ht="51" customHeight="1">
-      <c r="A28" s="45" t="inlineStr">
+      <c r="F27" s="30" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>APP_GRP</t>
         </is>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C28" s="31" t="inlineStr">
+      <c r="C28" s="30" t="inlineStr">
         <is>
           <t>Cấp thẩm quyền phê duyệt</t>
         </is>
@@ -1337,20 +1337,20 @@
           <t>B.APP_GRP</t>
         </is>
       </c>
-      <c r="F28" s="31" t="n"/>
-    </row>
-    <row r="29" ht="51" customHeight="1">
-      <c r="A29" s="45" t="inlineStr">
+      <c r="F28" s="30" t="n"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>LAST_APPROVAL_DATE</t>
         </is>
       </c>
-      <c r="B29" s="27" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C29" s="31" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>Ngày phê duyệt gần nhất</t>
         </is>
@@ -1365,20 +1365,20 @@
           <t>MAX(D.EXITDATE) WHERE D.WI_NAME = A.WI_NAME AND D.WORKSTEP IN ('CreditApprovalReview','CreditApproval','CreditCommittee') AND D.DECISION IN ('Submit','Send To HOSupport','Send To PostSanction','Submit To DisbursementMaker')</t>
         </is>
       </c>
-      <c r="F29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="51" customHeight="1">
-      <c r="A30" s="45" t="inlineStr">
+      <c r="F29" s="30" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>CUSTOMER_NAME</t>
         </is>
       </c>
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(150)</t>
         </is>
       </c>
-      <c r="C30" s="31" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
         <is>
           <t>Tên khách hàng vay chính</t>
         </is>
@@ -1393,20 +1393,20 @@
           <t>A.CUSTOMER_NAME</t>
         </is>
       </c>
-      <c r="F30" s="31" t="n"/>
-    </row>
-    <row r="31" ht="51" customHeight="1">
-      <c r="A31" s="45" t="inlineStr">
+      <c r="F30" s="30" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>APPROVAL_CONDITION</t>
         </is>
       </c>
-      <c r="B31" s="27" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C31" s="31" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
         <is>
           <t>Nhóm/cấp phê duyệt</t>
         </is>
@@ -1421,20 +1421,20 @@
           <t>A.APPROVAL_CONDITION</t>
         </is>
       </c>
-      <c r="F31" s="31" t="n"/>
-    </row>
-    <row r="32" ht="51" customHeight="1">
-      <c r="A32" s="45" t="inlineStr">
+      <c r="F31" s="30" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>APPROVER_TYPE</t>
         </is>
       </c>
-      <c r="B32" s="27" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C32" s="31" t="inlineStr">
+      <c r="C32" s="30" t="inlineStr">
         <is>
           <t>Loại cấp phê duyệt</t>
         </is>
@@ -1449,20 +1449,20 @@
           <t>A.APPROVER_TYPE</t>
         </is>
       </c>
-      <c r="F32" s="31" t="n"/>
-    </row>
-    <row r="33" ht="51" customHeight="1">
-      <c r="A33" s="45" t="inlineStr">
+      <c r="F32" s="30" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>APP_STATUS</t>
         </is>
       </c>
-      <c r="B33" s="27" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C33" s="31" t="inlineStr">
+      <c r="C33" s="30" t="inlineStr">
         <is>
           <t>Trạng thái hồ sơ</t>
         </is>
@@ -1477,20 +1477,20 @@
           <t>A.APP_STATUS</t>
         </is>
       </c>
-      <c r="F33" s="31" t="n"/>
-    </row>
-    <row r="34" ht="51" customHeight="1">
-      <c r="A34" s="45" t="inlineStr">
+      <c r="F33" s="30" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>RMEMAILID</t>
         </is>
       </c>
-      <c r="B34" s="27" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(250)</t>
         </is>
       </c>
-      <c r="C34" s="31" t="inlineStr">
+      <c r="C34" s="30" t="inlineStr">
         <is>
           <t>Email cán bộ RM</t>
         </is>
@@ -1505,20 +1505,20 @@
           <t>A.RMEMAILID</t>
         </is>
       </c>
-      <c r="F34" s="31" t="n"/>
-    </row>
-    <row r="35" ht="51" customHeight="1">
-      <c r="A35" s="45" t="inlineStr">
+      <c r="F34" s="30" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="B35" s="27" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(4000)</t>
         </is>
       </c>
-      <c r="C35" s="31" t="inlineStr">
+      <c r="C35" s="30" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
@@ -1533,20 +1533,20 @@
           <t>A.REMARKS</t>
         </is>
       </c>
-      <c r="F35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="51" customHeight="1">
-      <c r="A36" s="45" t="inlineStr">
+      <c r="F35" s="30" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>ZONE</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C36" s="31" t="inlineStr">
+      <c r="C36" s="30" t="inlineStr">
         <is>
           <t>Vùng miền quản lý tự khai</t>
         </is>
@@ -1561,20 +1561,20 @@
           <t>C.ZONE</t>
         </is>
       </c>
-      <c r="F36" s="31" t="n"/>
-    </row>
-    <row r="37" ht="51" customHeight="1">
-      <c r="A37" s="45" t="inlineStr">
+      <c r="F36" s="30" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>SALE_TYPE</t>
         </is>
       </c>
-      <c r="B37" s="27" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C37" s="31" t="inlineStr">
+      <c r="C37" s="30" t="inlineStr">
         <is>
           <t>Kênh bán hàng</t>
         </is>
@@ -1589,20 +1589,20 @@
           <t>C.SALE_TYPE</t>
         </is>
       </c>
-      <c r="F37" s="31" t="n"/>
-    </row>
-    <row r="38" ht="51" customHeight="1">
-      <c r="A38" s="45" t="inlineStr">
+      <c r="F37" s="30" t="n"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>BROKER_TYPE</t>
         </is>
       </c>
-      <c r="B38" s="27" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C38" s="31" t="inlineStr">
+      <c r="C38" s="30" t="inlineStr">
         <is>
           <t>Loại đối tác giới thiệu</t>
         </is>
@@ -1617,20 +1617,20 @@
           <t>C.BROKER_TYPE</t>
         </is>
       </c>
-      <c r="F38" s="31" t="n"/>
-    </row>
-    <row r="39" ht="51" customHeight="1">
-      <c r="A39" s="45" t="inlineStr">
+      <c r="F38" s="30" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>BROKER_ID</t>
         </is>
       </c>
-      <c r="B39" s="27" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C39" s="31" t="inlineStr">
+      <c r="C39" s="30" t="inlineStr">
         <is>
           <t>Mã đối tác giới thiệu</t>
         </is>
@@ -1645,20 +1645,20 @@
           <t>C.BROKER_ID</t>
         </is>
       </c>
-      <c r="F39" s="31" t="n"/>
-    </row>
-    <row r="40" ht="51" customHeight="1">
-      <c r="A40" s="45" t="inlineStr">
+      <c r="F39" s="30" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>BROKER_NAME</t>
         </is>
       </c>
-      <c r="B40" s="27" t="inlineStr">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C40" s="31" t="inlineStr">
+      <c r="C40" s="30" t="inlineStr">
         <is>
           <t>Tên đối tác giới thiệu</t>
         </is>
@@ -1673,20 +1673,20 @@
           <t>C.BROKER_NAME</t>
         </is>
       </c>
-      <c r="F40" s="31" t="n"/>
-    </row>
-    <row r="41" ht="51" customHeight="1">
-      <c r="A41" s="45" t="inlineStr">
+      <c r="F40" s="30" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>ACC_OFFICER</t>
         </is>
       </c>
-      <c r="B41" s="27" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C41" s="31" t="inlineStr">
+      <c r="C41" s="30" t="inlineStr">
         <is>
           <t>Mã Account Officer</t>
         </is>
@@ -1701,20 +1701,20 @@
           <t>C.ACC_OFFICER</t>
         </is>
       </c>
-      <c r="F41" s="31" t="n"/>
-    </row>
-    <row r="42" ht="51" customHeight="1">
-      <c r="A42" s="45" t="inlineStr">
+      <c r="F41" s="30" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>ACCOUNT_OFFICER_NAME</t>
         </is>
       </c>
-      <c r="B42" s="27" t="inlineStr">
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C42" s="31" t="inlineStr">
+      <c r="C42" s="30" t="inlineStr">
         <is>
           <t>Tên Account Officer</t>
         </is>
@@ -1729,20 +1729,20 @@
           <t>C.ACCOUNT_OFFICER_NAME</t>
         </is>
       </c>
-      <c r="F42" s="31" t="n"/>
-    </row>
-    <row r="43" ht="51" customHeight="1">
-      <c r="A43" s="45" t="inlineStr">
+      <c r="F42" s="30" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="36" t="inlineStr">
         <is>
           <t>EXISTING_CUSTOMER</t>
         </is>
       </c>
-      <c r="B43" s="27" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C43" s="31" t="inlineStr">
+      <c r="C43" s="30" t="inlineStr">
         <is>
           <t>Cờ khách hàng hiện hữu</t>
         </is>
@@ -1757,20 +1757,20 @@
           <t>C.EXISTING_CUSTOMER</t>
         </is>
       </c>
-      <c r="F43" s="31" t="n"/>
-    </row>
-    <row r="44" ht="51" customHeight="1">
-      <c r="A44" s="45" t="inlineStr">
+      <c r="F43" s="30" t="n"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="36" t="inlineStr">
         <is>
           <t>APPLICANT_CIF</t>
         </is>
       </c>
-      <c r="B44" s="27" t="inlineStr">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C44" s="31" t="inlineStr">
+      <c r="C44" s="30" t="inlineStr">
         <is>
           <t>Mã CIF khách hàng</t>
         </is>
@@ -1785,20 +1785,20 @@
           <t>C.APPLICANTCIF</t>
         </is>
       </c>
-      <c r="F44" s="31" t="n"/>
-    </row>
-    <row r="45" ht="51" customHeight="1">
-      <c r="A45" s="45" t="inlineStr">
+      <c r="F44" s="30" t="n"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="36" t="inlineStr">
         <is>
           <t>KYC1</t>
         </is>
       </c>
-      <c r="B45" s="27" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C45" s="31" t="inlineStr">
+      <c r="C45" s="30" t="inlineStr">
         <is>
           <t>Đơn vị/khối đang xử lý</t>
         </is>
@@ -1813,20 +1813,20 @@
           <t>C.KYC1</t>
         </is>
       </c>
-      <c r="F45" s="31" t="n"/>
-    </row>
-    <row r="46" ht="51" customHeight="1">
-      <c r="A46" s="45" t="inlineStr">
+      <c r="F45" s="30" t="n"/>
+    </row>
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" s="36" t="inlineStr">
         <is>
           <t>INTEREST_RATE_PCT</t>
         </is>
       </c>
-      <c r="B46" s="27" t="inlineStr">
+      <c r="B46" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C46" s="31" t="inlineStr">
+      <c r="C46" s="30" t="inlineStr">
         <is>
           <t>Lãi suất phê duyệt</t>
         </is>
@@ -1841,20 +1841,20 @@
           <t>TO_NUMBER(REGEXP_REPLACE(REGEXP_REPLACE(REPLACE(TRIM(F.CURRENT_RATE), '%', ''),'\.{2,}', '.'),'^\.([0-9]+\.)', '\1')DEFAULT NULL ON CONVERSION ERROR)</t>
         </is>
       </c>
-      <c r="F46" s="31" t="n"/>
-    </row>
-    <row r="47" ht="51" customHeight="1">
-      <c r="A47" s="45" t="inlineStr">
+      <c r="F46" s="30" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="36" t="inlineStr">
         <is>
           <t>LOAN_TO_VALUE</t>
         </is>
       </c>
-      <c r="B47" s="27" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C47" s="31" t="inlineStr">
+      <c r="C47" s="30" t="inlineStr">
         <is>
           <t>Tỷ lệ cho vay/TSBĐ</t>
         </is>
@@ -1869,20 +1869,20 @@
           <t>G.LOAN_TO_VALUE</t>
         </is>
       </c>
-      <c r="F47" s="31" t="n"/>
-    </row>
-    <row r="48" ht="51" customHeight="1">
-      <c r="A48" s="45" t="inlineStr">
+      <c r="F47" s="30" t="n"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="36" t="inlineStr">
         <is>
           <t>LOAN_OBJECTIVE</t>
         </is>
       </c>
-      <c r="B48" s="27" t="inlineStr">
+      <c r="B48" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C48" s="31" t="inlineStr">
+      <c r="C48" s="30" t="inlineStr">
         <is>
           <t>Mục đích vay</t>
         </is>
@@ -1897,20 +1897,20 @@
           <t>F.LOAN_OBJECTIVE</t>
         </is>
       </c>
-      <c r="F48" s="31" t="n"/>
-    </row>
-    <row r="49" ht="51" customHeight="1">
-      <c r="A49" s="45" t="inlineStr">
+      <c r="F48" s="30" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="36" t="inlineStr">
         <is>
           <t>TOTAL_INCOME</t>
         </is>
       </c>
-      <c r="B49" s="27" t="inlineStr">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C49" s="31" t="inlineStr">
+      <c r="C49" s="30" t="inlineStr">
         <is>
           <t>Tổng thu nhập khách hàng</t>
         </is>
@@ -1925,20 +1925,20 @@
           <t>H.TOT_INC_CALC</t>
         </is>
       </c>
-      <c r="F49" s="31" t="n"/>
-    </row>
-    <row r="50" ht="51" customHeight="1">
-      <c r="A50" s="45" t="inlineStr">
+      <c r="F49" s="30" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>SALARYFLAG</t>
         </is>
       </c>
-      <c r="B50" s="27" t="inlineStr">
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C50" s="31" t="inlineStr">
+      <c r="C50" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu từ lương</t>
         </is>
@@ -1953,20 +1953,20 @@
           <t>I.SALARYFLAG</t>
         </is>
       </c>
-      <c r="F50" s="31" t="n"/>
-    </row>
-    <row r="51" ht="51" customHeight="1">
-      <c r="A51" s="45" t="inlineStr">
+      <c r="F50" s="30" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="36" t="inlineStr">
         <is>
           <t>CARFLAG</t>
         </is>
       </c>
-      <c r="B51" s="27" t="inlineStr">
+      <c r="B51" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C51" s="31" t="inlineStr">
+      <c r="C51" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu thuê phương tiện</t>
         </is>
@@ -1981,20 +1981,20 @@
           <t>I.CARFLAG</t>
         </is>
       </c>
-      <c r="F51" s="31" t="n"/>
-    </row>
-    <row r="52" ht="51" customHeight="1">
-      <c r="A52" s="45" t="inlineStr">
+      <c r="F51" s="30" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="36" t="inlineStr">
         <is>
           <t>HOUSEFLAG</t>
         </is>
       </c>
-      <c r="B52" s="27" t="inlineStr">
+      <c r="B52" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C52" s="31" t="inlineStr">
+      <c r="C52" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu thuê nhà</t>
         </is>
@@ -2009,20 +2009,20 @@
           <t>I.HOUSEFLAG</t>
         </is>
       </c>
-      <c r="F52" s="31" t="n"/>
-    </row>
-    <row r="53" ht="51" customHeight="1">
-      <c r="A53" s="45" t="inlineStr">
+      <c r="F52" s="30" t="n"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="36" t="inlineStr">
         <is>
           <t>ENTERPRISSEFLAG</t>
         </is>
       </c>
-      <c r="B53" s="27" t="inlineStr">
+      <c r="B53" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C53" s="31" t="inlineStr">
+      <c r="C53" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu lợi nhuận DN</t>
         </is>
@@ -2037,20 +2037,20 @@
           <t>I.ENTERPRISSEFLAG</t>
         </is>
       </c>
-      <c r="F53" s="31" t="n"/>
-    </row>
-    <row r="54" ht="51" customHeight="1">
-      <c r="A54" s="45" t="inlineStr">
+      <c r="F53" s="30" t="n"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>DIVINGFLAG</t>
         </is>
       </c>
-      <c r="B54" s="27" t="inlineStr">
+      <c r="B54" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C54" s="31" t="inlineStr">
+      <c r="C54" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu cổ tức</t>
         </is>
@@ -2065,20 +2065,20 @@
           <t>I.DIVINGFLAG</t>
         </is>
       </c>
-      <c r="F54" s="31" t="n"/>
-    </row>
-    <row r="55" ht="51" customHeight="1">
-      <c r="A55" s="45" t="inlineStr">
+      <c r="F54" s="30" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="36" t="inlineStr">
         <is>
           <t>FAIMILYFLAG</t>
         </is>
       </c>
-      <c r="B55" s="27" t="inlineStr">
+      <c r="B55" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C55" s="31" t="inlineStr">
+      <c r="C55" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu kinh doanh hộ GĐ</t>
         </is>
@@ -2093,20 +2093,20 @@
           <t>I.FAIMILYFLAG</t>
         </is>
       </c>
-      <c r="F55" s="31" t="n"/>
-    </row>
-    <row r="56" ht="51" customHeight="1">
-      <c r="A56" s="45" t="inlineStr">
+      <c r="F55" s="30" t="n"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="36" t="inlineStr">
         <is>
           <t>NONLICFLAG</t>
         </is>
       </c>
-      <c r="B56" s="27" t="inlineStr">
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C56" s="31" t="inlineStr">
+      <c r="C56" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu KD không đăng ký</t>
         </is>
@@ -2121,20 +2121,20 @@
           <t>I.NONLICFLAG</t>
         </is>
       </c>
-      <c r="F56" s="31" t="n"/>
-    </row>
-    <row r="57" ht="51" customHeight="1">
-      <c r="A57" s="45" t="inlineStr">
+      <c r="F56" s="30" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="36" t="inlineStr">
         <is>
           <t>WAGESFLAG</t>
         </is>
       </c>
-      <c r="B57" s="27" t="inlineStr">
+      <c r="B57" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C57" s="31" t="inlineStr">
+      <c r="C57" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu tiền công</t>
         </is>
@@ -2149,20 +2149,20 @@
           <t>I.WAGESFLAG</t>
         </is>
       </c>
-      <c r="F57" s="31" t="n"/>
-    </row>
-    <row r="58" ht="51" customHeight="1">
-      <c r="A58" s="45" t="inlineStr">
+      <c r="F57" s="30" t="n"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="36" t="inlineStr">
         <is>
           <t>PENSIONFLAG</t>
         </is>
       </c>
-      <c r="B58" s="27" t="inlineStr">
+      <c r="B58" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C58" s="31" t="inlineStr">
+      <c r="C58" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu lương hưu</t>
         </is>
@@ -2177,20 +2177,20 @@
           <t>I.PENSIONFLAG</t>
         </is>
       </c>
-      <c r="F58" s="31" t="n"/>
-    </row>
-    <row r="59" ht="51" customHeight="1">
-      <c r="A59" s="45" t="inlineStr">
+      <c r="F58" s="30" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="36" t="inlineStr">
         <is>
           <t>OTHERFLAG</t>
         </is>
       </c>
-      <c r="B59" s="27" t="inlineStr">
+      <c r="B59" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C59" s="31" t="inlineStr">
+      <c r="C59" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu khác</t>
         </is>
@@ -2205,20 +2205,20 @@
           <t>I.OTHERFLAG</t>
         </is>
       </c>
-      <c r="F59" s="31" t="n"/>
-    </row>
-    <row r="60" ht="51" customHeight="1">
-      <c r="A60" s="45" t="inlineStr">
+      <c r="F59" s="30" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="36" t="inlineStr">
         <is>
           <t>PRODUCT_NAME</t>
         </is>
       </c>
-      <c r="B60" s="27" t="inlineStr">
+      <c r="B60" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C60" s="31" t="inlineStr">
+      <c r="C60" s="30" t="inlineStr">
         <is>
           <t>Tên sản phẩm vay</t>
         </is>
@@ -2233,20 +2233,20 @@
           <t>A.PRODUCT_NAME</t>
         </is>
       </c>
-      <c r="F60" s="31" t="n"/>
-    </row>
-    <row r="61" ht="51" customHeight="1">
-      <c r="A61" s="45" t="inlineStr">
+      <c r="F60" s="30" t="n"/>
+    </row>
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="36" t="inlineStr">
         <is>
           <t>C_PHONE_CREATE_FLAG</t>
         </is>
       </c>
-      <c r="B61" s="27" t="inlineStr">
+      <c r="B61" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(20)</t>
         </is>
       </c>
-      <c r="C61" s="31" t="inlineStr">
+      <c r="C61" s="30" t="inlineStr">
         <is>
           <t>Cờ phát sinh Xác minh ĐT</t>
         </is>
@@ -2261,20 +2261,20 @@
           <t>A.C_PHONE_CREATE_FLAG</t>
         </is>
       </c>
-      <c r="F61" s="31" t="n"/>
-    </row>
-    <row r="62" ht="51" customHeight="1">
-      <c r="A62" s="45" t="inlineStr">
+      <c r="F61" s="30" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="36" t="inlineStr">
         <is>
           <t>C_PHONE_DELETE_FLAG</t>
         </is>
       </c>
-      <c r="B62" s="27" t="inlineStr">
+      <c r="B62" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C62" s="31" t="inlineStr">
+      <c r="C62" s="30" t="inlineStr">
         <is>
           <t>Cờ xóa nhánh Xác minh ĐT</t>
         </is>
@@ -2289,20 +2289,20 @@
           <t>A.C_PHONE_DELETE_FLAG</t>
         </is>
       </c>
-      <c r="F62" s="31" t="n"/>
-    </row>
-    <row r="63" ht="51" customFormat="1" customHeight="1" s="15">
-      <c r="A63" s="45" t="inlineStr">
+      <c r="F62" s="30" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="36" t="inlineStr">
         <is>
           <t>C_FI_CREATE_FLAG</t>
         </is>
       </c>
-      <c r="B63" s="27" t="inlineStr">
+      <c r="B63" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(20)</t>
         </is>
       </c>
-      <c r="C63" s="31" t="inlineStr">
+      <c r="C63" s="30" t="inlineStr">
         <is>
           <t>Cờ phát sinh Thẩm định thực địa</t>
         </is>
@@ -2317,20 +2317,20 @@
           <t>A.C_FI_CREATE_FLAG</t>
         </is>
       </c>
-      <c r="F63" s="31" t="n"/>
-    </row>
-    <row r="64" ht="51" customHeight="1">
-      <c r="A64" s="45" t="inlineStr">
+      <c r="F63" s="30" t="n"/>
+    </row>
+    <row r="64" ht="30" customFormat="1" customHeight="1" s="15">
+      <c r="A64" s="36" t="inlineStr">
         <is>
           <t>C_FI_DELETE_FLAG</t>
         </is>
       </c>
-      <c r="B64" s="27" t="inlineStr">
+      <c r="B64" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C64" s="31" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>Cờ xóa nhánh Thẩm định thực địa</t>
         </is>
@@ -2345,20 +2345,20 @@
           <t>A.C_FI_DELETE_FLAG</t>
         </is>
       </c>
-      <c r="F64" s="31" t="n"/>
-    </row>
-    <row r="65" ht="51" customHeight="1">
-      <c r="A65" s="45" t="inlineStr">
+      <c r="F64" s="30" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="36" t="inlineStr">
         <is>
           <t>C_LEGAL_CREATE_FLAG</t>
         </is>
       </c>
-      <c r="B65" s="27" t="inlineStr">
+      <c r="B65" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(20)</t>
         </is>
       </c>
-      <c r="C65" s="31" t="inlineStr">
+      <c r="C65" s="30" t="inlineStr">
         <is>
           <t>Cờ phát sinh Thẩm định pháp chế</t>
         </is>
@@ -2373,20 +2373,20 @@
           <t>A.C_LEGAL_CREATE_FLAG</t>
         </is>
       </c>
-      <c r="F65" s="31" t="n"/>
-    </row>
-    <row r="66" ht="51" customHeight="1">
-      <c r="A66" s="45" t="inlineStr">
+      <c r="F65" s="30" t="n"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="36" t="inlineStr">
         <is>
           <t>C_LEGAL_DELETE_FLAG</t>
         </is>
       </c>
-      <c r="B66" s="27" t="inlineStr">
+      <c r="B66" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C66" s="31" t="inlineStr">
+      <c r="C66" s="30" t="inlineStr">
         <is>
           <t>Cờ xóa nhánh Thẩm định pháp chế</t>
         </is>
@@ -2401,20 +2401,20 @@
           <t>A.C_LEGAL_DELETE_FLAG</t>
         </is>
       </c>
-      <c r="F66" s="31" t="n"/>
-    </row>
-    <row r="67" ht="51" customHeight="1">
-      <c r="A67" s="45" t="inlineStr">
+      <c r="F66" s="30" t="n"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="36" t="inlineStr">
         <is>
           <t>REINITIATE</t>
         </is>
       </c>
-      <c r="B67" s="27" t="inlineStr">
+      <c r="B67" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(5)</t>
         </is>
       </c>
-      <c r="C67" s="31" t="inlineStr">
+      <c r="C67" s="30" t="inlineStr">
         <is>
           <t>Cờ khởi tạo lại</t>
         </is>
@@ -2429,20 +2429,20 @@
           <t>A.REINITIATE</t>
         </is>
       </c>
-      <c r="F67" s="31" t="n"/>
-    </row>
-    <row r="68" ht="51" customHeight="1">
-      <c r="A68" s="45" t="inlineStr">
+      <c r="F67" s="30" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="36" t="inlineStr">
         <is>
           <t>NORMALBRHOLD</t>
         </is>
       </c>
-      <c r="B68" s="27" t="inlineStr">
+      <c r="B68" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C68" s="31" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>Cờ hold ký HĐ không công chứng</t>
         </is>
@@ -2457,20 +2457,20 @@
           <t>A.NORMALBRHOLD</t>
         </is>
       </c>
-      <c r="F68" s="31" t="n"/>
-    </row>
-    <row r="69" ht="51" customHeight="1">
-      <c r="A69" s="45" t="inlineStr">
+      <c r="F68" s="30" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="36" t="inlineStr">
         <is>
           <t>REGBRHOLD</t>
         </is>
       </c>
-      <c r="B69" s="27" t="inlineStr">
+      <c r="B69" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C69" s="31" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>Cờ hold ký HĐ có công chứng</t>
         </is>
@@ -2485,20 +2485,20 @@
           <t>A.REGBRHOLD</t>
         </is>
       </c>
-      <c r="F69" s="31" t="n"/>
-    </row>
-    <row r="70" ht="51" customHeight="1">
-      <c r="A70" s="45" t="inlineStr">
+      <c r="F69" s="30" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="36" t="inlineStr">
         <is>
           <t>STP_FLAG</t>
         </is>
       </c>
-      <c r="B70" s="27" t="inlineStr">
+      <c r="B70" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C70" s="31" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>Cờ xử lý tự động STP</t>
         </is>
@@ -2513,20 +2513,20 @@
           <t>A.STP_FLAG</t>
         </is>
       </c>
-      <c r="F70" s="31" t="n"/>
-    </row>
-    <row r="71" ht="51" customHeight="1">
-      <c r="A71" s="45" t="inlineStr">
+      <c r="F70" s="30" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="36" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="B71" s="27" t="inlineStr">
+      <c r="B71" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C71" s="31" t="inlineStr">
+      <c r="C71" s="30" t="inlineStr">
         <is>
           <t>Cờ đủ điều kiện</t>
         </is>
@@ -2541,20 +2541,20 @@
           <t>A.ELIGIBLE</t>
         </is>
       </c>
-      <c r="F71" s="31" t="n"/>
-    </row>
-    <row r="72" ht="51" customHeight="1">
-      <c r="A72" s="45" t="inlineStr">
+      <c r="F71" s="30" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="36" t="inlineStr">
         <is>
           <t>TOTALNONELIGIBLE</t>
         </is>
       </c>
-      <c r="B72" s="27" t="inlineStr">
+      <c r="B72" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(5)</t>
         </is>
       </c>
-      <c r="C72" s="31" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>Số điều kiện không đạt</t>
         </is>
@@ -2569,20 +2569,20 @@
           <t>A.TOTALNONELIGIBLE</t>
         </is>
       </c>
-      <c r="F72" s="31" t="n"/>
-    </row>
-    <row r="73" ht="51" customHeight="1">
-      <c r="A73" s="45" t="inlineStr">
+      <c r="F72" s="30" t="n"/>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="36" t="inlineStr">
         <is>
           <t>CANCEL_REASON</t>
         </is>
       </c>
-      <c r="B73" s="27" t="inlineStr">
+      <c r="B73" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C73" s="31" t="inlineStr">
+      <c r="C73" s="30" t="inlineStr">
         <is>
           <t>Lý do hủy hồ sơ</t>
         </is>
@@ -2597,27 +2597,27 @@
           <t>A.REASON</t>
         </is>
       </c>
-      <c r="F73" s="31" t="n"/>
-    </row>
-    <row r="74" ht="51" customHeight="1">
-      <c r="A74" s="45" t="inlineStr">
+      <c r="F73" s="30" t="n"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="36" t="inlineStr">
         <is>
           <t>EFF_DATE</t>
         </is>
       </c>
-      <c r="B74" s="27" t="inlineStr">
+      <c r="B74" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C74" s="31" t="inlineStr">
+      <c r="C74" s="30" t="inlineStr">
         <is>
           <t>Ngày hiệu lực bản ghi</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t>Ngày bắt đầu hiệu lực của phiên bản bản ghi (SCD Type 2) — chỉ áp dụng cho các cột nghiệp vụ gốc SCD2, không áp dụng cho nhóm cột SCD1 bổ sung ở trên — CDC: so sánh bản ghi cũ/mới của A tại mỗi lần ETL chạy</t>
+          <t>Ngày bắt đầu hiệu lực của phiên bản bản ghi (SCD Type 2)</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
@@ -2625,20 +2625,20 @@
           <t>v_batch_date</t>
         </is>
       </c>
-      <c r="F74" s="31" t="n"/>
-    </row>
-    <row r="75" ht="51" customHeight="1">
-      <c r="A75" s="45" t="inlineStr">
+      <c r="F74" s="30" t="n"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="36" t="inlineStr">
         <is>
           <t>EXP_DATE</t>
         </is>
       </c>
-      <c r="B75" s="27" t="inlineStr">
+      <c r="B75" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C75" s="31" t="inlineStr">
+      <c r="C75" s="30" t="inlineStr">
         <is>
           <t>Ngày hết hiệu lực bản ghi</t>
         </is>
@@ -2653,13 +2653,14 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="F75" s="31" t="n"/>
-    </row>
+      <c r="F75" s="30" t="n"/>
+    </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="18" t="n"/>
       <c r="B77" s="18" t="n"/>
       <c r="C77" s="18" t="n"/>
-      <c r="D77" s="46" t="inlineStr">
+      <c r="D77" s="44" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
@@ -2667,10 +2668,10 @@
       <c r="E77" s="18" t="n"/>
       <c r="F77" s="18" t="n"/>
     </row>
-    <row r="78">
-      <c r="A78" s="30" t="n"/>
-      <c r="B78" s="30" t="n"/>
-      <c r="C78" s="31" t="n"/>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="29" t="n"/>
+      <c r="B78" s="29" t="n"/>
+      <c r="C78" s="30" t="n"/>
       <c r="D78" s="17" t="n"/>
       <c r="E78" s="14" t="inlineStr">
         <is>
@@ -2679,10 +2680,10 @@
       </c>
       <c r="F78" s="8" t="n"/>
     </row>
-    <row r="79">
-      <c r="A79" s="30" t="n"/>
-      <c r="B79" s="30" t="n"/>
-      <c r="C79" s="31" t="n"/>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="29" t="n"/>
+      <c r="B79" s="29" t="n"/>
+      <c r="C79" s="30" t="n"/>
       <c r="D79" s="17" t="n"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
@@ -2691,10 +2692,10 @@
       </c>
       <c r="F79" s="8" t="n"/>
     </row>
-    <row r="80">
-      <c r="A80" s="30" t="n"/>
-      <c r="B80" s="30" t="n"/>
-      <c r="C80" s="31" t="n"/>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="29" t="n"/>
+      <c r="B80" s="29" t="n"/>
+      <c r="C80" s="30" t="n"/>
       <c r="D80" s="17" t="n"/>
       <c r="E80" s="14" t="inlineStr">
         <is>
@@ -2703,10 +2704,10 @@
       </c>
       <c r="F80" s="8" t="n"/>
     </row>
-    <row r="81">
-      <c r="A81" s="30" t="n"/>
-      <c r="B81" s="30" t="n"/>
-      <c r="C81" s="31" t="n"/>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="29" t="n"/>
+      <c r="B81" s="29" t="n"/>
+      <c r="C81" s="30" t="n"/>
       <c r="D81" s="17" t="n"/>
       <c r="E81" s="14" t="inlineStr">
         <is>
@@ -2715,10 +2716,10 @@
       </c>
       <c r="F81" s="8" t="n"/>
     </row>
-    <row r="82">
-      <c r="A82" s="30" t="n"/>
-      <c r="B82" s="30" t="n"/>
-      <c r="C82" s="31" t="n"/>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="29" t="n"/>
+      <c r="B82" s="29" t="n"/>
+      <c r="C82" s="30" t="n"/>
       <c r="D82" s="17" t="n"/>
       <c r="E82" s="14" t="inlineStr">
         <is>
@@ -2727,10 +2728,10 @@
       </c>
       <c r="F82" s="8" t="n"/>
     </row>
-    <row r="83">
-      <c r="A83" s="30" t="n"/>
-      <c r="B83" s="30" t="n"/>
-      <c r="C83" s="31" t="n"/>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="29" t="n"/>
+      <c r="B83" s="29" t="n"/>
+      <c r="C83" s="30" t="n"/>
       <c r="D83" s="17" t="n"/>
       <c r="E83" s="14" t="inlineStr">
         <is>
@@ -2739,10 +2740,10 @@
       </c>
       <c r="F83" s="8" t="n"/>
     </row>
-    <row r="84">
-      <c r="A84" s="30" t="n"/>
-      <c r="B84" s="30" t="n"/>
-      <c r="C84" s="31" t="n"/>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="29" t="n"/>
+      <c r="B84" s="29" t="n"/>
+      <c r="C84" s="30" t="n"/>
       <c r="D84" s="17" t="n"/>
       <c r="E84" s="14" t="inlineStr">
         <is>
@@ -2752,7 +2753,7 @@
       <c r="F84" s="8" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:E70"/>
+  <autoFilter ref="A6:E71"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
